--- a/samples/ss_muarakarang_durikosambi_ingest.xlsx
+++ b/samples/ss_muarakarang_durikosambi_ingest.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -479,6 +480,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>UP2B Jakarta &amp; Banten</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Koreksi MKBRU dan DMGOT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Konfirmasi pengguna 2026-09-12; Buku Kerawanan 2026 hal.75-76 (PDF91-92). IBT MKBRU1,2 ke GIS; DKSBI1. DMGOT GIS ke DKSBI dan PIK. Interkoneksi GIS-GI digambar dua sirkit sesuai pasangan pada diagram sumber.</t>
         </is>
       </c>
     </row>
@@ -541,7 +554,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +574,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -575,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -669,6 +682,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Bus HV</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -676,7 +699,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Muarakarang (sisi 500 kV)</t>
+          <t>GITET Muarakarang Baru</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -703,11 +726,7 @@
           <t>Rawan</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="J2" s="3" t="n"/>
       <c r="K2" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -721,21 +740,21 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GIS Muarakarang Baru (sisi 500 kV)</t>
+          <t>PLTGU Muarakarang Unit 4 &amp; 5</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GIS MKBRU</t>
+          <t>PLTGU MK45</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
@@ -743,20 +762,16 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>500 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -765,21 +780,26 @@
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>MUARAKARANG</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>MKLMA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>PLTGU Muarakarang Unit 4 &amp; 5</t>
+          <t>PLTGU Muarakarang Blok 2</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>PLTGU MK45</t>
+          <t>PLTGU MK B2</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -820,16 +840,16 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>PLTGU Muarakarang Blok 2</t>
+          <t>PLTGU Muarakarang Blok 1</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>PLTGU MK B2</t>
+          <t>PLTGU MK B1</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -864,27 +884,27 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>MKLMA</t>
+          <t>MKBRU</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>PLTGU Muarakarang Blok 1</t>
+          <t>Durikosambi (sisi 500 kV)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>PLTGU MK B1</t>
+          <t>DKSBI</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
@@ -892,7 +912,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>500 kV</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
@@ -909,49 +929,48 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MUARAKARANG</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>MKBRU</t>
+          <t>DURIKOSAMBI</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Durikosambi (sisi 500 kV)</t>
+          <t>MKLMA</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>MKLMA</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>500 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -959,22 +978,22 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>DURIKOSAMBI</t>
+          <t>MUARAKARANG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>MKLMA</t>
+          <t>MKBRU (sisi 150 kV)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>MKLMA</t>
+          <t>MKBRU</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -998,7 +1017,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -1014,21 +1033,21 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>MKBRU (sisi 150 kV)</t>
+          <t>GIS Muarakarang Baru</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>MKBRU</t>
+          <t>GIS MKBRU</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
@@ -1063,16 +1082,16 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>GIS MKBRU (sisi 150 kV)</t>
+          <t>DKSBI (sisi 150 kV)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>GIS MKBRU</t>
+          <t>DKSBI</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1091,14 +1110,10 @@
       <c r="G10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1106,22 +1121,22 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MUARAKARANG</t>
+          <t>DURIKOSAMBI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>DKSBI (sisi 150 kV)</t>
+          <t>BDKMY</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>BDKMY</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1130,7 +1145,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1140,10 +1155,14 @@
       <c r="G11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="n"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1151,22 +1170,22 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>DURIKOSAMBI</t>
+          <t>MUARAKARANG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>BDKMY</t>
+          <t>ANGKE</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>BDKMY</t>
+          <t>ANGKE</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1185,14 +1204,10 @@
       <c r="G12" s="3" t="n"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1206,16 +1221,16 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ANGKE</t>
+          <t>Pantai Indah Kapuk (PIK)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>ANGKE</t>
+          <t>PINKA</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1251,16 +1266,16 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>PINKA</t>
+          <t>CKRNG</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>PINKA</t>
+          <t>CKRNG</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1290,22 +1305,22 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>MUARAKARANG</t>
+          <t>DURIKOSAMBI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>PINKA</t>
+          <t>KBJRK</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>PINKA</t>
+          <t>KBJRK</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1314,7 +1329,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1324,10 +1339,14 @@
       <c r="G15" s="3" t="n"/>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="n"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1341,21 +1360,21 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>CKRNG</t>
+          <t>GIS Daan Mogot</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>CKRNG</t>
+          <t>DMGOT</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -1386,16 +1405,16 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>KBJRK</t>
+          <t>KBSRH</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>KBJRK</t>
+          <t>KBSRH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1404,7 +1423,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1414,12 +1433,12 @@
       <c r="G17" s="3" t="n"/>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Rawan</t>
+          <t>Sangat Rawan</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -1429,22 +1448,22 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>DURIKOSAMBI</t>
+          <t>MUARAKARANG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>DMGOT</t>
+          <t>KTPNG</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>DMGOT</t>
+          <t>KTPNG</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1453,7 +1472,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1463,10 +1482,14 @@
       <c r="G18" s="3" t="n"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="n"/>
+          <t>Sangat Rawan</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>5;7</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1474,22 +1497,22 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>MUARAKARANG;DURIKOSAMBI</t>
+          <t>MUARAKARANG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>KBSRH</t>
+          <t>KRLMA</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>KBSRH</t>
+          <t>KRLMA</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1513,7 +1536,7 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -1529,21 +1552,21 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>KTPNG</t>
+          <t>ANCOL</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>KTPNG</t>
+          <t>ANCOL</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
@@ -1555,16 +1578,15 @@
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>5;7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1573,26 +1595,31 @@
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>MUARAKARANG</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>ANGKE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>KRLMA</t>
+          <t>GMLMA</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>KRLMA</t>
+          <t>GMLMA</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
@@ -1604,16 +1631,15 @@
         </is>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Sangat Rawan</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1622,21 +1648,26 @@
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t>MUARAKARANG</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>KBSRH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>ANCOL</t>
+          <t>MGBSR</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>ANCOL</t>
+          <t>MGBSR</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1674,27 +1705,27 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ANGKE</t>
+          <t>KTPNG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GMLMA</t>
+          <t>GIS PLTD Senayan</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>GMLMA</t>
+          <t>GIS PLTD SNY</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
@@ -1706,9 +1737,6 @@
         </is>
       </c>
       <c r="G23" s="3" t="n"/>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -1725,29 +1753,24 @@
           <t>MUARAKARANG</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>KBSRH</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>MGBSR</t>
+          <t>MPLMA</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>MGBSR</t>
+          <t>MPLMA</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
@@ -1759,15 +1782,16 @@
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="n"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1776,26 +1800,21 @@
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t>MUARAKARANG</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>KTPNG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GIS PLTD Senayan</t>
+          <t>KRBRU</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>GIS PLTD SNY</t>
+          <t>KRBRU</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1814,10 +1833,14 @@
       <c r="G25" s="3" t="n"/>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1825,22 +1848,22 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>MUARAKARANG</t>
+          <t>DURIKOSAMBI</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>MPLMA</t>
+          <t>CSW</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>MPLMA</t>
+          <t>CSW</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1849,7 +1872,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1859,14 +1882,10 @@
       <c r="G26" s="3" t="n"/>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1880,16 +1899,16 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>KRBRU</t>
+          <t>KARET</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>KRBRU</t>
+          <t>KARET</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1898,7 +1917,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -1908,14 +1927,10 @@
       <c r="G27" s="3" t="n"/>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1929,16 +1944,16 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CSW</t>
+          <t>SMBAS</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>CSW</t>
+          <t>SMBAS</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1947,7 +1962,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -1974,25 +1989,25 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>KARET</t>
+          <t>PNDAH</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>KARET</t>
+          <t>PNDAH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2000,6 +2015,9 @@
         </is>
       </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Normal</t>
@@ -2013,31 +2031,36 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>DURIKOSAMBI</t>
+          <t>MUARAKARANG</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SMBAS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>SMBAS</t>
+          <t>PLTD Senayan</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>SMBAS</t>
+          <t>PLTD SNY</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2061,107 +2084,144 @@
           <t>MUARAKARANG</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>GIS PLTD SNY</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>30</v>
-      </c>
+      <c r="A31" s="3" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>PNDAH</t>
+          <t>IBT 1 MKBRU</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>PNDAH</t>
+          <t>IBT 1 MKBRU</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>5</v>
-      </c>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" t="n">
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
+      <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
           <t>MUARAKARANG</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>SMBAS</t>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>GITET_MKBRU</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>GIS MKBRU</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>31</v>
-      </c>
+      <c r="A32" s="3" t="n"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PLTD Senayan</t>
+          <t>IBT 2 MKBRU</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>PLTD SNY</t>
+          <t>IBT 2 MKBRU</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>3</v>
-      </c>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n"/>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>DKI Jakarta</t>
-        </is>
-      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
           <t>MUARAKARANG</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>GIS PLTD SNY</t>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>GITET_MKBRU</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>GIS MKBRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n"/>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>IBT 1 DKSBI</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>IBT 1 DKSBI</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>DURIKOSAMBI</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>GITET_DKSBI</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>DKSBI</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3378,7 +3438,7 @@
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>SUTT Durikosambi - Duri Muara</t>
+          <t>SUTT Durikosambi - Daan Mogot</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3506,12 +3566,12 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>SUTT Kebon Jeruk - Pinang Kencana</t>
+          <t>SUTT Daan Mogot - PIK</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>KBJRK</t>
+          <t>DMGOT</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -3553,7 +3613,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>DURIKOSAMBI</t>
+          <t>MUARAKARANG;DURIKOSAMBI</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -3685,6 +3745,50 @@
       <c r="Q23" t="inlineStr">
         <is>
           <t>Tidak</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n"/>
+      <c r="B24" s="3" t="n"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Interkoneksi GIS MKBRU - GI MKBRU (incomer)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>GIS MKBRU</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>MKBRU</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n"/>
+      <c r="N24" s="3" t="n"/>
+      <c r="O24" s="3" t="n"/>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>MUARAKARANG</t>
         </is>
       </c>
     </row>
@@ -4011,4 +4115,110 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Nama GI</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Jumlah Sirkit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Tegangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DMGOT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GIS Daan Mogot</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PINKA</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MUARAKARANG</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PINKA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pantai Indah Kapuk (PIK)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DMGOT</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>DURIKOSAMBI</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/samples/ss_muarakarang_durikosambi_ingest.xlsx
+++ b/samples/ss_muarakarang_durikosambi_ingest.xlsx
@@ -4123,7 +4123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4144,15 +4144,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Tegangan</t>
         </is>
@@ -4174,15 +4179,15 @@
           <t>PINKA</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>MUARAKARANG</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
@@ -4204,15 +4209,15 @@
           <t>DMGOT</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>DURIKOSAMBI</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>150 kV</t>
         </is>
